--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96782</v>
+        <v>96784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96784</v>
+        <v>96790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96790</v>
+        <v>96792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96792</v>
+        <v>96793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96793</v>
+        <v>96799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2026 artfynd.xlsx
+++ b/artfynd/A 34540-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136730041</v>
       </c>
       <c r="B2" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
